--- a/students/ترابیfce1OK.xlsx
+++ b/students/ترابیfce1OK.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27328"/>
   <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89945209-3B44-4121-89A2-31FCF3D76111}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20730" windowHeight="11760"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -117,12 +118,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -466,23 +467,23 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I93"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G93"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="11" customWidth="1"/>
     <col min="5" max="6" width="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="41.5703125" customWidth="1"/>
+    <col min="7" max="7" width="41.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -505,7 +506,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>10067</v>
       </c>
@@ -526,7 +527,7 @@
       </c>
       <c r="G2" s="1"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>10083</v>
       </c>
@@ -546,10 +547,8 @@
         <v>12</v>
       </c>
       <c r="G3" s="1"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>10084</v>
       </c>
@@ -567,10 +566,8 @@
       </c>
       <c r="F4" s="1"/>
       <c r="G4" s="2"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>10065</v>
       </c>
@@ -590,9 +587,8 @@
         <v>9198431232</v>
       </c>
       <c r="G5" s="1"/>
-      <c r="H5" s="4"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>111391</v>
       </c>
@@ -612,9 +608,8 @@
         <v>9125425837</v>
       </c>
       <c r="G6" s="1"/>
-      <c r="H6" s="4"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>111879</v>
       </c>
@@ -634,9 +629,8 @@
         <v>9024325405</v>
       </c>
       <c r="G7" s="3"/>
-      <c r="H7" s="4"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>9731</v>
       </c>
@@ -656,9 +650,8 @@
         <v>9039072061</v>
       </c>
       <c r="G8" s="1"/>
-      <c r="H8" s="4"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>9917</v>
       </c>
@@ -680,9 +673,8 @@
       <c r="G9" s="1">
         <v>9904037184</v>
       </c>
-      <c r="H9" s="4"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>111199</v>
       </c>
@@ -702,451 +694,148 @@
         <v>9196747177</v>
       </c>
       <c r="G10" s="1"/>
-      <c r="H10" s="4"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
         <v>1622</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D11" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E11" s="1">
+      <c r="D11" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E11" s="2">
         <v>9386391340</v>
       </c>
-      <c r="F11" s="1">
+      <c r="F11" s="2">
         <v>9919331493</v>
       </c>
-      <c r="G11" s="1"/>
-      <c r="H11" s="4"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G12" s="1"/>
-      <c r="H12" s="4"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G13" s="1"/>
-      <c r="H13" s="4"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
-    </row>
-    <row r="17" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
-    </row>
-    <row r="18" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="4"/>
-    </row>
-    <row r="19" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="4"/>
-    </row>
-    <row r="20" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="4"/>
-    </row>
-    <row r="21" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="4"/>
-    </row>
-    <row r="22" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="4"/>
-    </row>
-    <row r="23" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="4"/>
-    </row>
-    <row r="24" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
-      <c r="G24" s="4"/>
-      <c r="H24" s="4"/>
-    </row>
-    <row r="25" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="E25" s="4"/>
-      <c r="F25" s="4"/>
-      <c r="G25" s="4"/>
-      <c r="H25" s="4"/>
-    </row>
-    <row r="26" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="E26" s="4"/>
-      <c r="F26" s="4"/>
-      <c r="G26" s="4"/>
-      <c r="H26" s="4"/>
-    </row>
-    <row r="27" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="E27" s="4"/>
-      <c r="F27" s="4"/>
-      <c r="G27" s="4"/>
-      <c r="H27" s="4"/>
-    </row>
-    <row r="28" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
-      <c r="F28" s="4"/>
-      <c r="G28" s="4"/>
-      <c r="H28" s="4"/>
-    </row>
-    <row r="29" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D29" s="4"/>
-      <c r="E29" s="4"/>
-      <c r="F29" s="4"/>
-      <c r="G29" s="4"/>
-      <c r="H29" s="4"/>
-    </row>
-    <row r="30" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D30" s="4"/>
-      <c r="E30" s="4"/>
-      <c r="F30" s="4"/>
-      <c r="G30" s="4"/>
-      <c r="H30" s="4"/>
-    </row>
-    <row r="31" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D31" s="4"/>
-      <c r="E31" s="4"/>
-      <c r="F31" s="4"/>
-      <c r="G31" s="4"/>
-      <c r="H31" s="4"/>
-    </row>
-    <row r="32" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D32" s="4"/>
-      <c r="E32" s="4"/>
-      <c r="F32" s="4"/>
-      <c r="G32" s="4"/>
-      <c r="H32" s="4"/>
-    </row>
-    <row r="33" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D33" s="4"/>
-      <c r="E33" s="4"/>
-      <c r="F33" s="4"/>
-      <c r="G33" s="4"/>
-      <c r="H33" s="4"/>
-    </row>
-    <row r="34" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D34" s="4"/>
-      <c r="E34" s="4"/>
-      <c r="F34" s="4"/>
-      <c r="G34" s="4"/>
-      <c r="H34" s="4"/>
-    </row>
-    <row r="35" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D35" s="4"/>
-      <c r="E35" s="4"/>
-      <c r="F35" s="4"/>
-      <c r="G35" s="4"/>
-      <c r="H35" s="4"/>
-    </row>
-    <row r="36" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D36" s="4"/>
-      <c r="E36" s="4"/>
-      <c r="F36" s="4"/>
-      <c r="G36" s="4"/>
-      <c r="H36" s="4"/>
-    </row>
-    <row r="37" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="E37" s="4"/>
-      <c r="F37" s="4"/>
-      <c r="G37" s="4"/>
-      <c r="H37" s="4"/>
-    </row>
-    <row r="38" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="E38" s="4"/>
-      <c r="F38" s="4"/>
-      <c r="G38" s="4"/>
-      <c r="H38" s="4"/>
-    </row>
-    <row r="39" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="E39" s="4"/>
-      <c r="F39" s="4"/>
-      <c r="G39" s="4"/>
-      <c r="H39" s="4"/>
-    </row>
-    <row r="40" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="E40" s="4"/>
-      <c r="F40" s="4"/>
-      <c r="G40" s="4"/>
-      <c r="H40" s="4"/>
-    </row>
-    <row r="41" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="E41" s="4"/>
-      <c r="F41" s="4"/>
-      <c r="G41" s="4"/>
-      <c r="H41" s="4"/>
-    </row>
-    <row r="42" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="E42" s="4"/>
-      <c r="F42" s="4"/>
-      <c r="G42" s="4"/>
-      <c r="H42" s="4"/>
-    </row>
-    <row r="43" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="E43" s="4"/>
-      <c r="F43" s="4"/>
-      <c r="G43" s="4"/>
-      <c r="H43" s="4"/>
-    </row>
-    <row r="44" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="E44" s="4"/>
-      <c r="F44" s="4"/>
-      <c r="G44" s="4"/>
-      <c r="H44" s="4"/>
-    </row>
-    <row r="45" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="E45" s="4"/>
-      <c r="F45" s="4"/>
-      <c r="G45" s="4"/>
-      <c r="H45" s="4"/>
-    </row>
-    <row r="46" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="E46" s="4"/>
-      <c r="F46" s="4"/>
-      <c r="G46" s="4"/>
-      <c r="H46" s="4"/>
-    </row>
-    <row r="47" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="E47" s="4"/>
-      <c r="F47" s="4"/>
-      <c r="G47" s="4"/>
-      <c r="H47" s="4"/>
-    </row>
-    <row r="48" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="E48" s="4"/>
-      <c r="F48" s="4"/>
-      <c r="G48" s="4"/>
-      <c r="H48" s="4"/>
-    </row>
-    <row r="49" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E49" s="4"/>
-      <c r="F49" s="4"/>
-      <c r="G49" s="4"/>
-      <c r="H49" s="4"/>
-    </row>
-    <row r="50" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E50" s="4"/>
-      <c r="F50" s="4"/>
-      <c r="G50" s="4"/>
-      <c r="H50" s="4"/>
-    </row>
-    <row r="51" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E51" s="4"/>
-      <c r="F51" s="4"/>
-      <c r="G51" s="4"/>
-      <c r="H51" s="4"/>
-    </row>
-    <row r="52" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E52" s="4"/>
-      <c r="F52" s="4"/>
-      <c r="G52" s="4"/>
-      <c r="H52" s="4"/>
-    </row>
-    <row r="53" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E53" s="4"/>
-      <c r="F53" s="4"/>
-      <c r="G53" s="4"/>
-      <c r="H53" s="4"/>
-    </row>
-    <row r="54" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E54" s="4"/>
-      <c r="F54" s="4"/>
-      <c r="G54" s="4"/>
-      <c r="H54" s="4"/>
-    </row>
-    <row r="55" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E55" s="4"/>
-      <c r="F55" s="4"/>
-      <c r="G55" s="4"/>
-      <c r="H55" s="4"/>
-    </row>
-    <row r="56" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E56" s="4"/>
-      <c r="F56" s="4"/>
-      <c r="G56" s="4"/>
-      <c r="H56" s="4"/>
-    </row>
-    <row r="57" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="G57" s="4"/>
-      <c r="H57" s="4"/>
-    </row>
-    <row r="58" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="G58" s="4"/>
-    </row>
-    <row r="59" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="G59" s="4"/>
-    </row>
-    <row r="60" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="G60" s="4"/>
-    </row>
-    <row r="61" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="G61" s="4"/>
-    </row>
-    <row r="62" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="G62" s="4"/>
-    </row>
-    <row r="63" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="G63" s="4"/>
-    </row>
-    <row r="64" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="G64" s="4"/>
-    </row>
-    <row r="65" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G65" s="4"/>
-    </row>
-    <row r="66" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G66" s="4"/>
-    </row>
-    <row r="67" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G67" s="4"/>
-    </row>
-    <row r="68" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G68" s="4"/>
-    </row>
-    <row r="69" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G69" s="4"/>
-    </row>
-    <row r="70" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G70" s="4"/>
-    </row>
-    <row r="71" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G71" s="4"/>
-    </row>
-    <row r="72" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G72" s="4"/>
-    </row>
-    <row r="73" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G73" s="4"/>
-    </row>
-    <row r="74" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G74" s="4"/>
-    </row>
-    <row r="75" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G75" s="4"/>
-    </row>
-    <row r="76" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G76" s="4"/>
-    </row>
-    <row r="77" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G77" s="4"/>
-    </row>
-    <row r="78" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G78" s="4"/>
-    </row>
-    <row r="79" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G79" s="4"/>
-    </row>
-    <row r="80" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G80" s="4"/>
-    </row>
-    <row r="81" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G81" s="4"/>
-    </row>
-    <row r="82" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G82" s="4"/>
-    </row>
-    <row r="83" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G83" s="4"/>
-    </row>
-    <row r="84" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G84" s="4"/>
-    </row>
-    <row r="85" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G85" s="4"/>
-    </row>
-    <row r="86" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G86" s="4"/>
-    </row>
-    <row r="87" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G87" s="4"/>
-    </row>
-    <row r="88" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G88" s="4"/>
-    </row>
-    <row r="89" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G89" s="4"/>
-    </row>
-    <row r="90" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G90" s="4"/>
-    </row>
-    <row r="91" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G91" s="4"/>
-    </row>
-    <row r="92" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G92" s="4"/>
-    </row>
-    <row r="93" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G93" s="4"/>
-    </row>
+      <c r="G11" s="2"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="4"/>
+      <c r="B12" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G12" s="4"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G13" s="4"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="17" x14ac:dyDescent="0.25"/>
+    <row r="18" x14ac:dyDescent="0.25"/>
+    <row r="19" x14ac:dyDescent="0.25"/>
+    <row r="20" x14ac:dyDescent="0.25"/>
+    <row r="21" x14ac:dyDescent="0.25"/>
+    <row r="22" x14ac:dyDescent="0.25"/>
+    <row r="23" x14ac:dyDescent="0.25"/>
+    <row r="24" x14ac:dyDescent="0.25"/>
+    <row r="25" x14ac:dyDescent="0.25"/>
+    <row r="26" x14ac:dyDescent="0.25"/>
+    <row r="27" x14ac:dyDescent="0.25"/>
+    <row r="28" x14ac:dyDescent="0.25"/>
+    <row r="29" x14ac:dyDescent="0.25"/>
+    <row r="30" x14ac:dyDescent="0.25"/>
+    <row r="31" x14ac:dyDescent="0.25"/>
+    <row r="32" x14ac:dyDescent="0.25"/>
+    <row r="33" x14ac:dyDescent="0.25"/>
+    <row r="34" x14ac:dyDescent="0.25"/>
+    <row r="35" x14ac:dyDescent="0.25"/>
+    <row r="36" x14ac:dyDescent="0.25"/>
+    <row r="37" x14ac:dyDescent="0.25"/>
+    <row r="38" x14ac:dyDescent="0.25"/>
+    <row r="39" x14ac:dyDescent="0.25"/>
+    <row r="40" x14ac:dyDescent="0.25"/>
+    <row r="41" x14ac:dyDescent="0.25"/>
+    <row r="42" x14ac:dyDescent="0.25"/>
+    <row r="43" x14ac:dyDescent="0.25"/>
+    <row r="44" x14ac:dyDescent="0.25"/>
+    <row r="45" x14ac:dyDescent="0.25"/>
+    <row r="46" x14ac:dyDescent="0.25"/>
+    <row r="47" x14ac:dyDescent="0.25"/>
+    <row r="48" x14ac:dyDescent="0.25"/>
+    <row r="49" x14ac:dyDescent="0.25"/>
+    <row r="50" x14ac:dyDescent="0.25"/>
+    <row r="51" x14ac:dyDescent="0.25"/>
+    <row r="52" x14ac:dyDescent="0.25"/>
+    <row r="53" x14ac:dyDescent="0.25"/>
+    <row r="54" x14ac:dyDescent="0.25"/>
+    <row r="55" x14ac:dyDescent="0.25"/>
+    <row r="56" x14ac:dyDescent="0.25"/>
+    <row r="57" x14ac:dyDescent="0.25"/>
+    <row r="58" x14ac:dyDescent="0.25"/>
+    <row r="59" x14ac:dyDescent="0.25"/>
+    <row r="60" x14ac:dyDescent="0.25"/>
+    <row r="61" x14ac:dyDescent="0.25"/>
+    <row r="62" x14ac:dyDescent="0.25"/>
+    <row r="63" x14ac:dyDescent="0.25"/>
+    <row r="64" x14ac:dyDescent="0.25"/>
+    <row r="65" x14ac:dyDescent="0.25"/>
+    <row r="66" x14ac:dyDescent="0.25"/>
+    <row r="67" x14ac:dyDescent="0.25"/>
+    <row r="68" x14ac:dyDescent="0.25"/>
+    <row r="69" x14ac:dyDescent="0.25"/>
+    <row r="70" x14ac:dyDescent="0.25"/>
+    <row r="71" x14ac:dyDescent="0.25"/>
+    <row r="72" x14ac:dyDescent="0.25"/>
+    <row r="73" x14ac:dyDescent="0.25"/>
+    <row r="74" x14ac:dyDescent="0.25"/>
+    <row r="75" x14ac:dyDescent="0.25"/>
+    <row r="76" x14ac:dyDescent="0.25"/>
+    <row r="77" x14ac:dyDescent="0.25"/>
+    <row r="78" x14ac:dyDescent="0.25"/>
+    <row r="79" x14ac:dyDescent="0.25"/>
+    <row r="80" x14ac:dyDescent="0.25"/>
+    <row r="81" x14ac:dyDescent="0.25"/>
+    <row r="82" x14ac:dyDescent="0.25"/>
+    <row r="83" x14ac:dyDescent="0.25"/>
+    <row r="84" x14ac:dyDescent="0.25"/>
+    <row r="85" x14ac:dyDescent="0.25"/>
+    <row r="86" x14ac:dyDescent="0.25"/>
+    <row r="87" x14ac:dyDescent="0.25"/>
+    <row r="88" x14ac:dyDescent="0.25"/>
+    <row r="89" x14ac:dyDescent="0.25"/>
+    <row r="90" x14ac:dyDescent="0.25"/>
+    <row r="91" x14ac:dyDescent="0.25"/>
+    <row r="92" x14ac:dyDescent="0.25"/>
+    <row r="93" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" r:id="rId1"/>
